--- a/Sample_Data/Tickets.xlsx
+++ b/Sample_Data/Tickets.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
   <si>
     <t>ticket_ID INT (PK)</t>
   </si>
@@ -125,6 +125,81 @@
   </si>
   <si>
     <t>Mouse cable chewed by rodent</t>
+  </si>
+  <si>
+    <t>Email sync issue on mobile</t>
+  </si>
+  <si>
+    <t>Projector bulb burnt out</t>
+  </si>
+  <si>
+    <t>VPN connection dropping</t>
+  </si>
+  <si>
+    <t>Keyboard unresponsive</t>
+  </si>
+  <si>
+    <t>Intranet portal 404 error</t>
+  </si>
+  <si>
+    <t>Mouse double-clicking</t>
+  </si>
+  <si>
+    <t>ERP system slow</t>
+  </si>
+  <si>
+    <t>Cannot print to Network Printer</t>
+  </si>
+  <si>
+    <t>New employee setup</t>
+  </si>
+  <si>
+    <t>Monitor flickering</t>
+  </si>
+  <si>
+    <t>Account locked out</t>
+  </si>
+  <si>
+    <t>Need access to shared folder</t>
+  </si>
+  <si>
+    <t>Software license expired</t>
+  </si>
+  <si>
+    <t>Desk phone no dial tone</t>
+  </si>
+  <si>
+    <t>Laptop running hot</t>
+  </si>
+  <si>
+    <t>Wi-Fi extremely slow</t>
+  </si>
+  <si>
+    <t>Missing Excel add-in</t>
+  </si>
+  <si>
+    <t>Phishing email reported</t>
+  </si>
+  <si>
+    <t>Headset microphone broken</t>
+  </si>
+  <si>
+    <t>Blue screen on startup</t>
+  </si>
+  <si>
+    <t>Cannot open PDF files</t>
+  </si>
+  <si>
+    <t>Update required for OS</t>
+  </si>
+  <si>
+    <t>Scanner not detected</t>
+  </si>
+  <si>
+    <t>Lost bitlocker recovery key</t>
+  </si>
+  <si>
+    <t>Guest Wi-Fi password request</t>
   </si>
 </sst>
 </file>
@@ -1208,6 +1283,767 @@
         <v>2.0</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>1026.0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>46239.552083333336</v>
+      </c>
+      <c r="G27" s="2">
+        <v>102.0</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>1027.0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>46239.572916666664</v>
+      </c>
+      <c r="F28" s="3">
+        <v>46239.604166666664</v>
+      </c>
+      <c r="G28" s="2">
+        <v>101.0</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>1028.0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>46239.583333333336</v>
+      </c>
+      <c r="G29" s="2">
+        <v>104.0</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>1029.0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E30" s="3">
+        <v>46239.59027777778</v>
+      </c>
+      <c r="F30" s="3">
+        <v>46239.600694444445</v>
+      </c>
+      <c r="G30" s="2">
+        <v>103.0</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>1030.0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E31" s="3">
+        <v>46239.604166666664</v>
+      </c>
+      <c r="G31" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>1031.0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>46239.625</v>
+      </c>
+      <c r="F32" s="3">
+        <v>46239.635416666664</v>
+      </c>
+      <c r="G32" s="2">
+        <v>101.0</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>1032.0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>46239.63888888889</v>
+      </c>
+      <c r="G33" s="2">
+        <v>102.0</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>1033.0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>46239.65625</v>
+      </c>
+      <c r="F34" s="3">
+        <v>46239.67361111111</v>
+      </c>
+      <c r="G34" s="2">
+        <v>103.0</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>1034.0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>46240.333333333336</v>
+      </c>
+      <c r="G35" s="2">
+        <v>104.0</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>1035.0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E36" s="3">
+        <v>46240.354166666664</v>
+      </c>
+      <c r="F36" s="3">
+        <v>46240.375</v>
+      </c>
+      <c r="G36" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>1036.0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E37" s="3">
+        <v>46240.364583333336</v>
+      </c>
+      <c r="F37" s="3">
+        <v>46240.37152777778</v>
+      </c>
+      <c r="G37" s="2">
+        <v>101.0</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>1037.0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E38" s="3">
+        <v>46240.385416666664</v>
+      </c>
+      <c r="G38" s="2">
+        <v>102.0</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>1038.0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>46240.395833333336</v>
+      </c>
+      <c r="G39" s="2">
+        <v>103.0</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J39" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>1039.0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="D40" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>46240.416666666664</v>
+      </c>
+      <c r="F40" s="3">
+        <v>46240.4375</v>
+      </c>
+      <c r="G40" s="2">
+        <v>104.0</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J40" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>1040.0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>46240.427083333336</v>
+      </c>
+      <c r="G41" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J41" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>1041.0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>46240.447916666664</v>
+      </c>
+      <c r="G42" s="2">
+        <v>101.0</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="J42" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>1042.0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>46240.458333333336</v>
+      </c>
+      <c r="F43" s="3">
+        <v>46240.47222222222</v>
+      </c>
+      <c r="G43" s="2">
+        <v>102.0</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>1043.0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>46240.479166666664</v>
+      </c>
+      <c r="G44" s="2">
+        <v>103.0</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J44" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>1044.0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="D45" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>46240.541666666664</v>
+      </c>
+      <c r="F45" s="3">
+        <v>46240.552083333336</v>
+      </c>
+      <c r="G45" s="2">
+        <v>104.0</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J45" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>1045.0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>46240.5625</v>
+      </c>
+      <c r="G46" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J46" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>1046.0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>46240.583333333336</v>
+      </c>
+      <c r="F47" s="3">
+        <v>46240.59722222222</v>
+      </c>
+      <c r="G47" s="2">
+        <v>101.0</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J47" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>1047.0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="D48" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>46240.59375</v>
+      </c>
+      <c r="G48" s="2">
+        <v>102.0</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="J48" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>1048.0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46240.614583333336</v>
+      </c>
+      <c r="F49" s="3">
+        <v>46240.631944444445</v>
+      </c>
+      <c r="G49" s="2">
+        <v>103.0</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="J49" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>1049.0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="D50" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E50" s="3">
+        <v>46240.625</v>
+      </c>
+      <c r="G50" s="2">
+        <v>104.0</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J50" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>1050.0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E51" s="3">
+        <v>46240.645833333336</v>
+      </c>
+      <c r="F51" s="3">
+        <v>46240.649305555555</v>
+      </c>
+      <c r="G51" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J51" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
